--- a/data/trans_dic/IP12B$estomago-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$estomago-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,9</t>
+          <t>0,0; 42,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,09</t>
+          <t>0,0; 38,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,05</t>
+          <t>0,0; 22,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,05</t>
+          <t>0,0; 17,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,41</t>
+          <t>0,0; 47,86</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,05</t>
+          <t>0,0; 13,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,21</t>
+          <t>0,0; 15,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,21</t>
+          <t>0,0; 9,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,62</t>
+          <t>0,0; 14,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,86</t>
+          <t>0,0; 6,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,03</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,98</t>
+          <t>1,05; 9,87</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,25</t>
+          <t>0,0; 39,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,55</t>
+          <t>0,0; 21,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,28</t>
+          <t>0,0; 15,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,59</t>
+          <t>0,0; 33,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 24,22</t>
+          <t>2,45; 26,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,58</t>
+          <t>0,0; 12,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,18</t>
+          <t>0,0; 12,59</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,15</t>
+          <t>1,01; 9,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,7</t>
+          <t>1,01; 9,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,37</t>
+          <t>1,38; 11,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 6,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 14,57</t>
+          <t>1,46; 13,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,42</t>
+          <t>1,48; 8,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,3</t>
+          <t>0,48; 4,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,91</t>
+          <t>1,79; 9,16</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2412</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2745</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2239</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2500</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2930</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4221</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1177</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1677</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2854</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4138</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4119</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5445</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4223</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3625</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>718; 6729</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1744</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3363</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3436</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2520</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3286</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>452; 4946</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3377</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3269</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1548</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1747</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3584</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4315</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>445; 4283</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3991</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>556; 5010</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>642; 5413</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4104</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>700; 6422</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1340; 7752</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>601; 5842</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1840; 9437</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$estomago-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$estomago-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,67</t>
+          <t>0,0; 39,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,95</t>
+          <t>0,0; 37,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,41</t>
+          <t>0,0; 22,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,12</t>
+          <t>0,0; 18,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,86</t>
+          <t>0,0; 44,75</t>
         </is>
       </c>
     </row>
@@ -798,22 +798,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,01</t>
+          <t>0,0; 11,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,42</t>
+          <t>0,0; 15,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,09</t>
+          <t>0,0; 8,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,97</t>
+          <t>0,0; 15,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,87</t>
+          <t>1,0; 9,87</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,12</t>
+          <t>0,0; 40,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,23</t>
+          <t>0,0; 21,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,06</t>
+          <t>0,0; 15,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,34</t>
+          <t>0,0; 29,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 26,81</t>
+          <t>2,42; 24,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,33</t>
+          <t>0,0; 13,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,59</t>
+          <t>0,0; 12,57</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,76</t>
+          <t>1,02; 9,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,09</t>
+          <t>1,0; 8,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 11,59</t>
+          <t>1,38; 10,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,46</t>
+          <t>0,0; 7,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,42</t>
+          <t>1,48; 15,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,56</t>
+          <t>1,47; 7,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,68</t>
+          <t>0,48; 4,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 9,16</t>
+          <t>1,48; 8,64</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2412</t>
+          <t>0; 2246</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2745</t>
+          <t>0; 2647</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2500</t>
+          <t>0; 2514</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2930</t>
+          <t>0; 3242</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4221</t>
+          <t>0; 3946</t>
         </is>
       </c>
     </row>
@@ -1479,37 +1479,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4138</t>
+          <t>0; 3742</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4835</t>
+          <t>0; 4789</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4119</t>
+          <t>0; 3707</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5445</t>
+          <t>0; 5580</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4223</t>
+          <t>0; 4225</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3625</t>
+          <t>0; 3352</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>718; 6729</t>
+          <t>679; 6732</t>
         </is>
       </c>
     </row>
@@ -1632,22 +1632,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3363</t>
+          <t>0; 3459</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3436</t>
+          <t>0; 3399</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2520</t>
+          <t>0; 2516</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3286</t>
+          <t>0; 2930</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1662,17 +1662,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>452; 4946</t>
+          <t>447; 4481</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3377</t>
+          <t>0; 3685</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3269</t>
+          <t>0; 3264</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>445; 4283</t>
+          <t>447; 3956</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3991</t>
+          <t>0; 3363</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>556; 5010</t>
+          <t>549; 4661</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>642; 5413</t>
+          <t>643; 4849</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4104</t>
+          <t>0; 4514</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>700; 6422</t>
+          <t>708; 7410</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1340; 7752</t>
+          <t>1329; 7216</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>601; 5842</t>
+          <t>605; 5908</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1840; 9437</t>
+          <t>1520; 8903</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$estomago-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$estomago-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39,82%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>8,02%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 48,09</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 39,9</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 37,55</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,54</t>
+          <t>0,0; 21,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,95</t>
+          <t>0,0; 18,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,75</t>
+          <t>0,0; 39,41</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,7%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 13,21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 8,21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 15,62</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,76</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 15,28</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,18</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,34</t>
+          <t>0,0; 11,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,93</t>
+          <t>0,0; 6,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 5,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,87</t>
+          <t>1,03; 9,98</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>12,73%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,13%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,41%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,23</t>
+          <t>0,0; 32,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,73</t>
+          <t>0,0; 41,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 18,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 24,28</t>
+          <t>2,42; 24,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,45</t>
+          <t>0,0; 11,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,57</t>
+          <t>0,0; 11,18</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,53%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,17%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,02</t>
+          <t>1,38; 10,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,49</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,46</t>
+          <t>1,47; 14,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,38</t>
+          <t>1,0; 9,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,1</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 15,48</t>
+          <t>1,0; 8,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,97</t>
+          <t>1,48; 8,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,73</t>
+          <t>0,48; 4,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,64</t>
+          <t>1,48; 8,91</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>454</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2246</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 3390</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2239</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2255</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2647</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2239</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2514</t>
+          <t>0; 2349</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3242</t>
+          <t>0; 3088</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3946</t>
+          <t>0; 3476</t>
         </is>
       </c>
     </row>
@@ -1363,27 +1363,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1677</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1177</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1387</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1677</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0; 4140</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3719</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5682</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3742</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4789</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3707</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5580</t>
+          <t>0; 3516</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4225</t>
+          <t>0; 4181</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3352</t>
+          <t>0; 4041</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>679; 6732</t>
+          <t>699; 6807</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1094</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>571</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3459</t>
+          <t>0; 3213</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3399</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2516</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2930</t>
+          <t>0; 3547</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3488</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3058</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>447; 4481</t>
+          <t>447; 4469</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3685</t>
+          <t>0; 3173</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3264</t>
+          <t>0; 2904</t>
         </is>
       </c>
     </row>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1548</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1747</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1338</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2568</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>447; 3956</t>
+          <t>643; 4841</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3363</t>
+          <t>0; 4478</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>549; 4661</t>
+          <t>705; 6971</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>643; 4849</t>
+          <t>440; 4013</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4514</t>
+          <t>0; 2934</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>708; 7410</t>
+          <t>550; 4798</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1329; 7216</t>
+          <t>1336; 7631</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>605; 5908</t>
+          <t>603; 5364</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1520; 8903</t>
+          <t>1520; 9176</t>
         </is>
       </c>
     </row>
